--- a/survey_templates/048_ngo_community_trust_survey--survey_templates.xlsx
+++ b/survey_templates/048_ngo_community_trust_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HH:MM:SS AM/PM</t>
+          <t>HH -MM -SS AM/PM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What time did you last contact us?</t>
+          <t>Time Of Last Contact</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HH:MM:SS AM/PM</t>
+          <t>HH -MM -SS AM/PM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Do you have an email address to contact you?</t>
+          <t>Email Response2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you have a phone number we can contact you with?</t>
+          <t>Phone Number2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Please provide more details about your last contact with us</t>
+          <t>Last Contact Details2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
